--- a/mainWidget/mainWidget/src/database/计算模型-爆炸冲击波试验.xlsx
+++ b/mainWidget/mainWidget/src/database/计算模型-爆炸冲击波试验.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\git\GFApp\mainWidget\mainWidget\src\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717E0101-FF76-493D-AF1D-A853448C8203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB57F32-79D2-422F-AD50-34F34AC83F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1571" uniqueCount="1406">
   <si>
     <t>序号</t>
   </si>
@@ -1768,6 +1768,3706 @@
   </si>
   <si>
     <t>-0.3219</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>2553.0620+0.0070*B+0.0000*C+0.4576*D+0.2132*E-0.0138*F+0.0000*G+2.5186*H+0.1624*I+0.7770*J-3.1974*K+18.8946*L+0.0013*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2553.0620</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0070</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4576</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2132</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0138</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.5186</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1624</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7770</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-3.1974</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18.8946</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>120.7648+0.0235*B+0.0000*C-1.3923*D-0.2448*E-0.0446*F+0.0000*G-6.9916*H+0.0312*I-3.4083*J-6.8464*K+65.8163*L+0.0073*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>120.7648</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0235</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.3923</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.2448</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0446</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-6.9916</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0312</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-3.4083</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-6.8464</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>65.8163</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0073</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1468.4193-0.0486*B+0.0000*C-0.4035*D+0.0141*E-0.1000*F+0.0000*G+9.9665*H-0.0636*I-1.8687*J-3.7092*K+85.4691*L+0.0128*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1468.4193</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0486</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.4035</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0141</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.9665</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0636</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.8687</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-3.7092</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>85.4691</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1164.3589+0.0485*B+0.0000*C-0.8921*D+0.0279*E-0.1760*F+0.0000*G-10.8431*H+0.0191*I+0.7046*J-0.7172*K-14.5629*L+0.0054*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1164.3589</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0485</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.8921</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0279</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1760</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-10.8431</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0191</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7046</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.7172</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-14.5629</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0054</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1164.3589-0.0181*B+0.0000*C-0.3430*D+0.1475*E+0.0405*F+0.0000*G-16.1540*H+0.0323*I-2.1020*J-4.0003*K+22.4078*L+0.0394*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0181</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.3430</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1475</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-16.1540</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0323</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2.1020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-4.0003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22.4078</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0394</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3651.3012-0.0233*B+0.0000*C-0.2336*D+0.0452*E+0.0999*F+0.0000*G-0.4741*H-0.0206*I-3.9037*J-6.0101*K+32.6173*L+0.0477*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3651.3012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0233</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.2336</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0452</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0999</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.4741</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0206</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-3.9037</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-6.0101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>32.6173</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0477</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1115.7767+0.0564*B+0.0000*C+0.2510*D-0.0925*E+0.0422*F+0.0000*G+24.1623*H-0.0051*I+1.0250*J-11.5196*K+33.0939*L+0.0153*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1115.7767</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0564</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2510</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0925</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0422</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24.1623</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0051</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.0250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-11.5196</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>33.0939</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0153</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>542.1072+0.0170*B+0.0000*C-1.4460*D-0.0325*E+0.0418*F+0.0000*G+23.4277*H-0.0551*I-3.1597*J-3.3224*K+37.8466*L+0.0215*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>542.1072</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0170</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.4460</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0325</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0418</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23.4277</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0551</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-3.1597</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-3.3224</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>37.8466</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0215</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-41.0535+0.0352*B+0.0000*C+0.0599*D+0.1350*E-0.0578*F+0.0000*G+1.3764*H-0.0420*I-4.7959*J-0.2344*K+4.5854*L+0.0132*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-41.0535</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0352</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0599</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1350</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0578</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.3764</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0420</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-4.7959</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.2344</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.5854</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0132</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>704.9106-0.0482*B+0.0000*C-0.3141*D-0.0499*E-0.0672*F+0.0000*G+3.4083*H+0.0406*I+1.0250*J-0.7048*K+4.4072*L+0.0112*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>704.9106</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0482</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.3141</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0499</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0672</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.4083</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0406</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.7048</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.4072</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0112</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1164.3589+0.0119*B+0.0000*C+0.0333*D+0.3458*E-0.0099*F+0.0000*G+9.0609*H-0.0049*I-4.0594*J+3.0426*K+29.5373*L+0.0333*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0119</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0333</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3458</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0099</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.0609</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0049</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-4.0594</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.0426</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>29.5373</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1000.4511+0.0736*B+0.0000*C-1.0229*D+0.0812*E+0.2141*F+0.0000*G-6.7194*H-0.0601*I-0.8911*J-3.3290*K-87.5065*L+0.0148*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1000.4511</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0736</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.0229</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0812</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2141</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-6.7194</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0601</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.8911</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-3.3290</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-87.5065</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0148</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1164.3589+0.0335*B+0.0000*C-0.6744*D+0.2170*E-0.0654*F+0.0000*G+1.4448*H+0.0830*I-4.2147*J-0.5001*K+57.7592*L-0.0118*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0335</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.6744</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2170</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0654</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.4448</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0830</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-4.2147</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.5001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>57.7592</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0118</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1764.3698+0.0242*B+0.0000*C+0.5545*D-0.1760*E-0.1159*F+0.0000*G+11.7526*H+0.0295*I-0.5143*J-0.0396*K-43.2509*L+0.0190*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1764.3698</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0242</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5545</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1159</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11.7526</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0295</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.5143</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-43.2509</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0190</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2038.4169-0.0179*B+0.0000*C+1.3375*D+0.0653*E-0.1038*F+0.0000*G+13.3967*H-0.1024*I+0.8261*J+3.1036*K-50.4007*L+0.0377*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2038.4169</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0179</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.3375</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0653</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1038</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.3967</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8261</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.1036</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-50.4007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0377</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2340.9452+0.0485*B+0.0000*C+1.3599*D-0.0362*E-0.0626*F+0.0000*G-5.4856*H-0.0859*I-1.3326*J-0.0601*K+5.3801*L+0.0342*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2340.9452</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.3599</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0362</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0626</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-5.4856</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0859</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.3326</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.3801</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0342</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1330.6199+0.0758*B+0.0000*C-0.2014*D+0.3821*E+0.0670*F+0.0000*G-5.0904*H-0.1124*I+0.0652*J-2.2453*K+27.6091*L+0.0252*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1330.6199</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0758</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.2014</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3821</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0670</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-5.0904</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1124</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0652</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2.2453</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>27.6091</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1113.7075-0.0236*B+0.0000*C-1.1045*D-0.0645*E+0.0887*F+0.0000*G+7.9929*H-0.1305*I-0.7074*J+0.1108*K-53.6119*L+0.0170*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1113.7075</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0236</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.1045</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0645</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0887</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.9929</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1305</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.7074</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-53.6119</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1444.8670-0.0364*B+0.0000*C+0.2482*D+0.0775*E+0.1100*F+0.0000*G+18.2483*H-0.1442*I-3.4827*J+0.6129*K+17.4320*L+0.0262*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1444.8670</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0364</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2482</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0775</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18.2483</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1442</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-3.4827</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6129</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.4320</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0262</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11034.4202+0.0377*B+0.0000*C+0.8101*D+0.1330*E+0.0695*F+0.0000*G+1.5277*H+0.0774*I-3.0706*J-2.2970*K-33.3560*L+0.0152*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11034.4202</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1330</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0695</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5277</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0774</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-3.0706</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2.2970</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-33.3560</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0152</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7147.3880-0.0613*B+0.0000*C+0.4855*D-0.2290*E-0.0361*F+0.0000*G+18.6776*H+0.0053*I-3.8322*J-4.1489*K+25.8604*L-0.0055*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7147.3880</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0613</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4855</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.2290</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0361</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18.6776</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-3.8322</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-4.1489</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25.8604</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1844.7975+0.0150*B+0.0000*C-0.4809*D+0.3008*E+0.0678*F+0.0000*G-18.3131*H+0.0180*I-2.7932*J+1.9187*K-48.9692*L+0.0102*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1844.7975</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0150</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.4809</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0678</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-18.3131</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0180</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2.7932</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.9187</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-48.9692</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2573.9699+0.0504*B+0.0000*C-0.8773*D-0.0487*E-0.0364*F+0.0000*G-2.6010*H+0.1817*I-0.1284*J-6.2604*K+37.9716*L+0.0673*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2573.9699</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0504</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.8773</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0487</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2.6010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1817</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1284</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-6.2604</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>37.9716</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0673</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3907.0172-0.0527*B+0.0000*C-0.3600*D+0.1771*E-0.0583*F+0.0000*G+10.7985*H+0.0790*I-3.4555*J-1.6108*K-173.4419*L-0.0118*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3907.0172</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0527</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.3600</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1771</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0583</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.7985</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0790</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-3.4555</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.6108</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-173.4419</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>659.4688-0.0409*B+0.0000*C+1.1690*D-0.2033*E-0.0331*F+0.0000*G+6.9749*H+0.1481*I-4.7268*J+3.1213*K-8.1642*L-0.0118*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>659.4688</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0409</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.1690</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.2033</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.9749</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1481</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-4.7268</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.1213</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-8.1642</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2465.5936+0.0216*B+0.0000*C-0.4438*D+0.0083*E-0.0280*F+0.0000*G+6.7645*H+0.0673*I+1.0250*J-6.1711*K+99.7402*L-0.0118*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2465.5936</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0216</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.4438</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0280</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.7645</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-6.1711</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>99.7402</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>914.1687+0.0384*B+0.0000*C+0.1927*D-0.0894*E-0.0113*F+0.0000*G-0.6429*H-0.0624*I+0.9823*J+0.0013*K-43.9058*L+0.0361*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>914.1687</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0384</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1927</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0894</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0113</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.6429</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0624</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9823</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-43.9058</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0361</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2074.3716+0.0481*B+0.0000*C+0.4446*D-0.1185*E-0.0444*F+0.0000*G+14.5049*H+0.0619*I-1.1923*J-0.9264*K+56.2608*L-0.0020*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2074.3716</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0481</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4446</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1185</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0444</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14.5049</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0619</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.1923</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.9264</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>56.2608</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2680.3910+0.0043*B+0.0000*C-0.1675*D+0.1534*E+0.0858*F+0.0000*G+15.3136*H+0.1340*I-1.0876*J+1.2589*K-24.4556*L+0.0214*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2680.3910</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0043</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1675</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1534</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0858</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15.3136</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1340</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.0876</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.2589</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-24.4556</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0214</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>968.8626+0.0172*B+0.0000*C+0.4197*D-0.1170*E+0.2049*F+0.0000*G-6.9084*H-0.1272*I+1.0250*J+1.6835*K+23.0404*L+0.0291*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>968.8626</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0172</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4197</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1170</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2049</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-6.9084</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1272</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.6835</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23.0404</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0291</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1266.8112-0.0258*B+0.0000*C+0.0445*D-0.0971*E+0.0999*F+0.0000*G+3.5821*H-0.0869*I-1.9429*J+0.2177*K-37.3392*L-0.0079*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1266.8112</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0258</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0971</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.5821</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0869</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.9429</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2177</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-37.3392</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0079</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1913.6100+0.0236*B+0.0000*C-0.3764*D-0.0680*E+0.0300*F+0.0000*G-12.3074*H-0.1473*I-2.9347*J-2.2065*K+7.1194*L+0.0508*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1913.6100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0236</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.3764</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0680</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-12.3074</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1473</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2.9347</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2.2065</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.1194</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0508</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3465.2468+0.0061*B+0.0000*C-0.0240*D-0.1430*E+0.0065*F+0.0000*G+1.8527*H+0.0321*I-3.2065*J+0.6296*K+69.2265*L+0.0103*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3465.2468</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0240</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1430</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0065</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.8527</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0321</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-3.2065</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6296</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>69.2265</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2312.9710+0.0428*B+0.0000*C-0.3001*D+0.0300*E+0.0094*F+0.0000*G+6.5710*H-0.0815*I-1.0788*J+0.5469*K+65.0790*L+0.0376*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2312.9710</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0428</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.3001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0094</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.5710</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0815</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.0788</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5469</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>65.0790</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0376</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6739.3041-0.0202*B+0.0000*C+0.6199*D+0.0243*E+0.2141*F+0.0000*G-4.4937*H-0.0884*I-2.6373*J-9.6005*K-35.4091*L-0.0063*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6739.3041</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0202</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6199</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0243</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-4.4937</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0884</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2.6373</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-9.6005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-35.4091</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0063</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1677.8379+0.0278*B+0.0000*C+1.3450*D+0.1325*E-0.0460*F+0.0000*G-5.5943*H+0.0497*I-4.4380*J+5.7078*K+51.2679*L+0.0011*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1677.8379</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0278</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.3450</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1325</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0460</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-5.5943</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0497</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-4.4380</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.7078</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>51.2679</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1164.3589+0.0715*B+0.0000*C-0.0930*D+0.1730*E-0.1417*F+0.0000*G-1.9421*H-0.0008*I-1.0227*J-3.1223*K+22.9758*L-0.0118*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0715</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0930</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1730</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1417</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.9421</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.0227</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-3.1223</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22.9758</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>937.9386+0.0182*B+0.0000*C+0.3614*D+0.0988*E-0.0975*F+0.0000*G-13.3581*H+0.1311*I-0.3099*J-4.2773*K+70.1625*L+0.0161*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>937.9386</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0182</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3614</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0988</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0975</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-13.3581</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1311</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.3099</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-4.2773</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70.1625</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0161</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4278.0922+0.0159*B+0.0000*C+1.4784*D+0.2460*E-0.0152*F+0.0000*G+17.2440*H+0.0656*I+1.0250*J-5.1150*K+26.1884*L+0.0401*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4278.0922</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.4784</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2460</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0152</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.2440</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0656</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-5.1150</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.1884</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0401</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1164.3589-0.0381*B+0.0000*C-1.4833*D-0.0396*E+0.0757*F+0.0000*G+23.7265*H+0.0063*I+1.0250*J-6.7218*K-95.2693*L+0.0117*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0381</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.4833</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0757</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23.7265</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0063</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-6.7218</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-95.2693</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0117</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2268.3751+0.0116*B+0.0000*C-1.5037*D-0.0141*E-0.1144*F+0.0000*G+13.5569*H+0.0367*I-3.4879*J-3.3692*K-62.5255*L+0.0115*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2268.3751</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0116</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.5037</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0141</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1144</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.5569</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0367</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-3.4879</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-3.3692</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-62.5255</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0115</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3711.6059-0.0296*B+0.0000*C+0.3539*D-0.0763*E-0.0663*F+0.0000*G+4.0710*H-0.1087*I-2.5231*J-6.0166*K+91.1849*L+0.0140*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3711.6059</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0296</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3539</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0763</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0663</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.0710</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1087</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2.5231</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-6.0166</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>91.1849</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0140</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-470.5914+0.0222*B+0.0000*C-0.0914*D-0.0327*E+0.0660*F+0.0000*G+14.6296*H-0.0563*I-2.5784*J-2.4450*K-125.6938*L-0.0118*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-470.5914</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0222</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0914</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0327</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0660</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14.6296</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2.5784</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2.4450</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-125.6938</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4752.1387+0.0841*B+0.0000*C-0.1901*D+0.0797*E+0.0375*F+0.0000*G+42.9807*H+0.1147*I-1.4596*J-5.0786*K-90.3420*L+0.0183*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4752.1387</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0841</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1901</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0797</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0375</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>42.9807</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1147</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.4596</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-5.0786</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-90.3420</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0183</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-613.6953-0.0485*B+0.0000*C-0.4773*D-0.1541*E+0.1668*F+0.0000*G+16.1456*H-0.0022*I+1.0250*J-1.0810*K-52.4645*L+0.0520*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-613.6953</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0485</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.4773</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1541</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1668</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16.1456</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0022</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.0810</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-52.4645</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0520</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2659.6998-0.0318*B+0.0000*C-0.1477*D-0.1251*E-0.1218*F+0.0000*G+16.6896*H+0.1966*I-4.6337*J+0.7984*K-41.7573*L+0.0007*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2659.6998</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0318</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1477</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1251</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16.6896</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1966</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-4.6337</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7984</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-41.7573</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-199.3421-0.0243*B+0.0000*C+0.0248*D-0.1188*E+0.0337*F+0.0000*G+4.7646*H-0.0261*I-3.4071*J-3.6127*K+29.7130*L+0.0259*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-199.3421</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0243</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0248</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1188</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0337</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.7646</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0261</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-3.4071</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-3.6127</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>29.7130</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0259</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1164.3589+0.0173*B+0.0000*C+0.5325*D-0.2370*E+0.0593*F+0.0000*G-2.7145*H+0.0578*I-3.0467*J-8.3658*K-91.4143*L+0.0143*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0173</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5325</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.2370</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0593</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2.7145</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0578</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-3.0467</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-8.3658</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-91.4143</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0143</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1954.1345-0.0261*B+0.0000*C+0.4511*D-0.2359*E+0.0020*F+0.0000*G-9.4121*H-0.0689*I-1.0216*J-4.7105*K-28.2318*L+0.0388*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1954.1345</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4511</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.2359</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-9.4121</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0689</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.0216</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-4.7105</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-28.2318</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0388</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-160.1651+0.0491*B+0.0000*C-0.8263*D+0.0732*E+0.1437*F+0.0000*G-18.3131*H-0.0840*I+0.3015*J-2.1663*K+10.1814*L-0.0023*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-160.1651</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0491</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.8263</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0732</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1437</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0840</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3015</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2.1663</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.1814</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0023</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1516.5919+0.0063*B+0.0000*C+0.8333*D+0.0343*E+0.0400*F+0.0000*G+0.3478*H-0.0519*I-2.2206*J+0.1462*K-30.0835*L+0.0205*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1516.5919</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8333</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0343</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3478</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2.2206</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1462</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-30.0835</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0205</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6542.7336+0.0506*B+0.0000*C-0.2458*D+0.1678*E-0.0301*F+0.0000*G-18.3131*H-0.1059*I-5.8133*J-2.7409*K-7.7482*L+0.0559*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6542.7336</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.2458</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1678</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0301</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1059</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-5.8133</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2.7409</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-7.7482</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0559</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2123.9753+0.0035*B+0.0000*C+0.5889*D-0.3134*E+0.0304*F+0.0000*G+14.7928*H-0.1546*I+1.0250*J-0.0704*K-29.7940*L+0.0292*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2123.9753</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0035</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5889</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.3134</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0304</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14.7928</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1546</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0704</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-29.7940</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0292</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7036.2775+0.0209*B+0.0000*C+0.1691*D-0.0664*E-0.0717*F+0.0000*G+15.5191*H-0.0901*I-0.9613*J-3.2291*K+15.6627*L+0.0216*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7036.2775</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0209</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1691</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0664</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0717</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15.5191</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0901</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.9613</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-3.2291</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15.6627</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3919.8420-0.0090*B+0.0000*C-0.2052*D-0.1396*E-0.0335*F+0.0000*G+9.9861*H+0.0771*I-3.4436*J+1.9852*K+60.2243*L+0.0237*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3919.8420</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0090</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.2052</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1396</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0335</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.9861</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0771</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-3.4436</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.9852</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>60.2243</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0237</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6040.8172-0.0204*B+0.0000*C-0.9093*D-0.2524*E+0.1489*F+0.0000*G+13.3699*H-0.0071*I-0.4407*J-5.7364*K+115.6361*L+0.0164*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6040.8172</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0204</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.9093</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.2524</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1489</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.3699</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0071</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.4407</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-5.7364</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>115.6361</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0164</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1574.2249+0.0444*B+0.0000*C+0.3372*D+0.0300*E-0.0661*F+0.0000*G+11.1362*H+0.1938*I+1.0250*J+4.7856*K-34.6701*L-0.0118*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1574.2249</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0444</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3372</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0661</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11.1362</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1938</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.7856</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-34.6701</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>979.8715+0.0154*B+0.0000*C+0.7802*D-0.2403*E+0.1520*F+0.0000*G+3.4484*H-0.0456*I-3.6683*J-7.7852*K+33.1583*L+0.0150*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>979.8715</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0154</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7802</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.2403</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1520</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.4484</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0456</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-3.6683</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-7.7852</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>33.1583</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1164.3589-0.0430*B+0.0000*C-0.2528*D+0.2338*E-0.0162*F+0.0000*G-12.9799*H-0.0268*I-1.8213*J-11.8181*K-11.4443*L+0.0072*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0430</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.2528</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2338</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0162</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-12.9799</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0268</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.8213</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-11.8181</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-11.4443</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0072</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3057.2206+0.0929*B+0.0000*C+0.8036*D-0.0395*E-0.0958*F+0.0000*G+36.8067*H+0.0048*I-1.1052*J-1.4738*K+1.3845*L+0.0094*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3057.2206</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0929</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8036</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0395</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0958</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>36.8067</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0048</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.1052</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.4738</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.3845</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-152.0026-0.0106*B+0.0000*C-0.0339*D-0.0782*E-0.0588*F+0.0000*G+6.6780*H-0.0278*I+1.0250*J-11.6404*K+46.7982*L+0.0449*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-152.0026</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0106</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0339</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0782</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0588</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.6780</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0278</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-11.6404</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>46.7982</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0449</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1164.3589-0.0018*B+0.0000*C-0.2786*D-0.2001*E-0.0649*F+0.0000*G-8.1854*H+0.1803*I+1.0250*J+3.5408*K+27.9991*L-0.0118*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0018</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.2786</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.2001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0649</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-8.1854</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1803</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.5408</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>27.9991</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-27.8111+0.0341*B+0.0000*C-0.8931*D+0.0990*E-0.0144*F+0.0000*G+0.8004*H+0.0724*I-0.0303*J-2.7775*K+50.2457*L-0.0118*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-27.8111</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0341</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.8931</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0990</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0144</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0724</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0303</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2.7775</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50.2457</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2854.3596+0.0386*B+0.0000*C-0.2339*D+0.0444*E-0.1094*F+0.0000*G+16.6633*H-0.0205*I-2.4458*J+2.6795*K-44.4870*L-0.0118*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2854.3596</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0386</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.2339</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1094</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16.6633</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0205</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2.4458</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.6795</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-44.4870</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1164.3589+0.0392*B+0.0000*C-0.9352*D+0.2459*E-0.1875*F+0.0000*G+26.0971*H+0.0205*I-1.3816*J-3.4894*K+11.6042*L+0.0121*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0392</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.9352</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2459</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1875</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.0971</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.3816</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-3.4894</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11.6042</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0121</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4086.0362+0.0179*B+0.0000*C+0.0983*D-0.0528*E+0.0029*F+0.0000*G+9.1373*H-0.1786*I-4.5078*J+1.4962*K+0.0009*L+0.0084*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4086.0362</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0179</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0983</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0528</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.1373</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1786</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-4.5078</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.4962</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1344.3478+0.0280*B+0.0000*C-0.4002*D-0.1113*E+0.0266*F+0.0000*G-6.5708*H+0.0410*I-5.3931*J+2.6027*K+15.3383*L+0.0196*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1344.3478</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0280</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.4002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1113</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0266</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-6.5708</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0410</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-5.3931</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.6027</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15.3383</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0196</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3781.2272+0.0850*B+0.0000*C+0.7225*D-0.2612*E-0.1121*F+0.0000*G-2.2528*H+0.0014*I+0.1531*J-4.1893*K+0.8092*L-0.0062*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3781.2272</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0850</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7225</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.2612</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1121</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2.2528</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1531</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-4.1893</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8092</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0062</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-247.6721-0.0478*B+0.0000*C-0.6772*D-0.1922*E-0.0835*F+0.0000*G+18.2463*H-0.0998*I+1.0250*J+0.5288*K+0.7110*L-0.0088*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-247.6721</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0478</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.6772</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1922</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0835</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18.2463</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0998</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5288</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7110</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0088</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3067.5910-0.0119*B+0.0000*C+0.0779*D+0.3595*E-0.0008*F+0.0000*G+19.4143*H-0.0742*I-1.2274*J+5.4730*K-40.5539*L+0.0594*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3067.5910</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0779</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3595</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>19.4143</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0742</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.2274</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.4730</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-40.5539</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0594</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3086.3986-0.0113*B+0.0000*C+0.4466*D+0.1356*E+0.0667*F+0.0000*G-13.7991*H-0.0767*I-1.7583*J-1.6685*K+22.8651*L+0.0176*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3086.3986</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4466</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1356</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0667</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-13.7991</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.7583</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.6685</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22.8651</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0176</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1164.3589+0.0294*B+0.0000*C+0.4308*D+0.0774*E+0.1098*F+0.0000*G+15.5629*H+0.0463*I-1.3153*J-7.8088*K+13.1536*L+0.0184*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0294</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4308</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1098</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15.5629</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0463</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.3153</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-7.8088</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.1536</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0184</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1984.0979-0.0422*B+0.0000*C-0.7912*D+0.1470*E+0.0045*F+0.0000*G+13.7013*H+0.0016*I-1.0657*J+2.2510*K-34.9156*L+0.0156*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1984.0979</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0422</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.7912</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1470</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0045</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.7013</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0016</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.0657</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.2510</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-34.9156</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0156</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>129.4950-0.0058*B+0.0000*C-0.2336*D+0.0298*E-0.0368*F+0.0000*G+20.7148*H-0.0941*I-1.6068*J-3.0823*K+64.8672*L+0.0181*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>129.4950</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0058</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0298</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0368</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20.7148</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0941</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-1.6068</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-3.0823</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>64.8672</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0181</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3905.4485-0.0512*B+0.0000*C+0.1827*D+0.1239*E+0.0160*F+0.0000*G+18.3909*H-0.0550*I+1.0250*J+7.5169*K-27.1279*L+0.0017*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3905.4485</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0512</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1827</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0160</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18.3909</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0550</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.5169</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-27.1279</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0017</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4970.7681+0.0813*B+0.0000*C-0.3879*D-0.0608*E-0.0183*F+0.0000*G-11.0417*H-0.0966*I-3.6484*J-4.3520*K-10.4475*L+0.0191*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4970.7681</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0813</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.3879</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0183</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-11.0417</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0966</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-3.6484</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-4.3520</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-10.4475</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5216.2006-0.0301*B+0.0000*C+0.7008*D-0.0317*E+0.0036*F+0.0000*G+13.6197*H-0.1177*I-0.1848*J-0.7362*K+16.3475*L+0.0205*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5216.2006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0317</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0036</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.6197</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1177</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1848</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.7362</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16.3475</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7502.8187-0.0146*B+0.0000*C-0.3938*D-0.0894*E-0.0440*F+0.0000*G-2.4063*H+0.1219*I+1.0250*J-3.5894*K-50.9940*L+0.0251*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7502.8187</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0146</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.3938</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0440</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2.4063</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1219</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-3.5894</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-50.9940</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0251</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-97.8218+0.0404*B+0.0000*C+0.1363*D-0.2153*E+0.1537*F+0.0000*G+27.3113*H-0.0649*I-2.1085*J-0.2741*K+8.3164*L+0.0299*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-97.8218</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0404</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1363</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.2153</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1537</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>27.3113</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2.1085</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.2741</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8.3164</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0299</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6377.9690+0.0054*B+0.0000*C-0.5869*D-0.1961*E-0.0605*F+0.0000*G+4.9735*H+0.1847*I-2.4330*J-0.5143*K-9.5192*L+0.0434*M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6377.9690</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.5869</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.1961</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.0605</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.9735</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1847</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-2.4330</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-9.5192</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0434</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2128,7 +5828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O121"/>
   <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
     <col min="3" max="15" width="9.23046875" style="3"/>
@@ -4061,6 +7761,3766 @@
         <v>151</v>
       </c>
     </row>
+    <row r="42" spans="1:15">
+      <c r="A42" t="s">
+        <v>461</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="E42" s="2">
+        <v>0</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="I42" s="2">
+        <v>0</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="L42" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="M42" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="N42" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="O42" s="4" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="A43" t="s">
+        <v>462</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="E43" s="2">
+        <v>0</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="I43" s="2">
+        <v>0</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="M43" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="N43" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="O43" s="4" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
+      <c r="A44" t="s">
+        <v>463</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="E44" s="2">
+        <v>0</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="I44" s="2">
+        <v>0</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="M44" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="N44" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="O44" s="4" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45" t="s">
+        <v>464</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="I45" s="2">
+        <v>0</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="L45" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="M45" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="O45" s="4" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" t="s">
+        <v>465</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="E46" s="2">
+        <v>0</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="I46" s="2">
+        <v>0</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="L46" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="M46" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="N46" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="O46" s="4" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="A47" t="s">
+        <v>466</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="E47" s="2">
+        <v>0</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="I47" s="2">
+        <v>0</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="L47" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="M47" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="N47" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="O47" s="4" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
+      <c r="A48" t="s">
+        <v>467</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="E48" s="2">
+        <v>0</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="I48" s="2">
+        <v>0</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="M48" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="N48" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="O48" s="4" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
+      <c r="A49" t="s">
+        <v>468</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="E49" s="2">
+        <v>0</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="I49" s="2">
+        <v>0</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="L49" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="M49" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="N49" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="O49" s="4" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
+      <c r="A50" t="s">
+        <v>469</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="E50" s="2">
+        <v>0</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="I50" s="2">
+        <v>0</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="L50" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="M50" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="N50" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="O50" s="4" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
+      <c r="A51" t="s">
+        <v>470</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="E51" s="2">
+        <v>0</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="I51" s="2">
+        <v>0</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="L51" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="M51" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="N51" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="O51" s="4" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
+      <c r="A52" t="s">
+        <v>471</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="E52" s="2">
+        <v>0</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="I52" s="2">
+        <v>0</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="L52" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="M52" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="N52" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="O52" s="4" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
+      <c r="A53" t="s">
+        <v>472</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="E53" s="2">
+        <v>0</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="I53" s="2">
+        <v>0</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="L53" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="M53" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="N53" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="O53" s="4" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
+      <c r="A54" t="s">
+        <v>473</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="E54" s="2">
+        <v>0</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="I54" s="2">
+        <v>0</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="L54" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="M54" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="N54" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="O54" s="4" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15">
+      <c r="A55" t="s">
+        <v>474</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="E55" s="2">
+        <v>0</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="I55" s="2">
+        <v>0</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="L55" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="M55" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="N55" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="O55" s="4" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15">
+      <c r="A56" t="s">
+        <v>475</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="E56" s="2">
+        <v>0</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>702</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="I56" s="2">
+        <v>0</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="L56" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="M56" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="N56" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="O56" s="4" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15">
+      <c r="A57" t="s">
+        <v>476</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="E57" s="2">
+        <v>0</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="I57" s="2">
+        <v>0</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="L57" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="M57" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="N57" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="O57" s="4" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15">
+      <c r="A58" t="s">
+        <v>477</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="E58" s="2">
+        <v>0</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="I58" s="2">
+        <v>0</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="L58" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="M58" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="N58" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="O58" s="4" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15">
+      <c r="A59" t="s">
+        <v>478</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="E59" s="2">
+        <v>0</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="I59" s="2">
+        <v>0</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="L59" s="4" t="s">
+        <v>740</v>
+      </c>
+      <c r="M59" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="N59" s="4" t="s">
+        <v>741</v>
+      </c>
+      <c r="O59" s="4" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15">
+      <c r="A60" t="s">
+        <v>479</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="E60" s="2">
+        <v>0</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>746</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="I60" s="2">
+        <v>0</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="L60" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="M60" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="N60" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="O60" s="4" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15">
+      <c r="A61" t="s">
+        <v>480</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>754</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="E61" s="2">
+        <v>0</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>757</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="I61" s="2">
+        <v>0</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="L61" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="M61" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="N61" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="O61" s="4" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15">
+      <c r="A62" t="s">
+        <v>481</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>766</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="E62" s="2">
+        <v>0</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>769</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="I62" s="2">
+        <v>0</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="L62" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="M62" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="N62" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="O62" s="4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15">
+      <c r="A63" t="s">
+        <v>482</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>777</v>
+      </c>
+      <c r="E63" s="2">
+        <v>0</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>778</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>779</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="I63" s="2">
+        <v>0</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="K63" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="L63" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="M63" s="4" t="s">
+        <v>784</v>
+      </c>
+      <c r="N63" s="4" t="s">
+        <v>785</v>
+      </c>
+      <c r="O63" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15">
+      <c r="A64" t="s">
+        <v>483</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>787</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>788</v>
+      </c>
+      <c r="E64" s="2">
+        <v>0</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>789</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="I64" s="2">
+        <v>0</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>791</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="L64" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="M64" s="4" t="s">
+        <v>794</v>
+      </c>
+      <c r="N64" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="O64" s="4" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15">
+      <c r="A65" t="s">
+        <v>484</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>798</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="E65" s="2">
+        <v>0</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>802</v>
+      </c>
+      <c r="I65" s="2">
+        <v>0</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>803</v>
+      </c>
+      <c r="K65" s="4" t="s">
+        <v>804</v>
+      </c>
+      <c r="L65" s="4" t="s">
+        <v>805</v>
+      </c>
+      <c r="M65" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="N65" s="4" t="s">
+        <v>807</v>
+      </c>
+      <c r="O65" s="4" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15">
+      <c r="A66" t="s">
+        <v>485</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>809</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>810</v>
+      </c>
+      <c r="E66" s="2">
+        <v>0</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="I66" s="2">
+        <v>0</v>
+      </c>
+      <c r="J66" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="K66" s="4" t="s">
+        <v>814</v>
+      </c>
+      <c r="L66" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="M66" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="N66" s="4" t="s">
+        <v>817</v>
+      </c>
+      <c r="O66" s="4" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15">
+      <c r="A67" t="s">
+        <v>486</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>819</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="E67" s="2">
+        <v>0</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>822</v>
+      </c>
+      <c r="I67" s="2">
+        <v>0</v>
+      </c>
+      <c r="J67" s="4" t="s">
+        <v>823</v>
+      </c>
+      <c r="K67" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="L67" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="M67" s="4" t="s">
+        <v>824</v>
+      </c>
+      <c r="N67" s="4" t="s">
+        <v>825</v>
+      </c>
+      <c r="O67" s="4" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15">
+      <c r="A68" t="s">
+        <v>487</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>826</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>827</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>828</v>
+      </c>
+      <c r="E68" s="2">
+        <v>0</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>829</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>831</v>
+      </c>
+      <c r="I68" s="2">
+        <v>0</v>
+      </c>
+      <c r="J68" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="K68" s="4" t="s">
+        <v>833</v>
+      </c>
+      <c r="L68" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="M68" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="N68" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="O68" s="4" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15">
+      <c r="A69" t="s">
+        <v>488</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>839</v>
+      </c>
+      <c r="E69" s="2">
+        <v>0</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>841</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="I69" s="2">
+        <v>0</v>
+      </c>
+      <c r="J69" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="K69" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="L69" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="M69" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="N69" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="O69" s="4" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15">
+      <c r="A70" t="s">
+        <v>489</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>849</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>851</v>
+      </c>
+      <c r="E70" s="2">
+        <v>0</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>852</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>854</v>
+      </c>
+      <c r="I70" s="2">
+        <v>0</v>
+      </c>
+      <c r="J70" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="K70" s="4" t="s">
+        <v>856</v>
+      </c>
+      <c r="L70" s="4" t="s">
+        <v>857</v>
+      </c>
+      <c r="M70" s="4" t="s">
+        <v>858</v>
+      </c>
+      <c r="N70" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="O70" s="4" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15">
+      <c r="A71" t="s">
+        <v>490</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>861</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>862</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>863</v>
+      </c>
+      <c r="E71" s="2">
+        <v>0</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>864</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>865</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>866</v>
+      </c>
+      <c r="I71" s="2">
+        <v>0</v>
+      </c>
+      <c r="J71" s="4" t="s">
+        <v>867</v>
+      </c>
+      <c r="K71" s="4" t="s">
+        <v>868</v>
+      </c>
+      <c r="L71" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="M71" s="4" t="s">
+        <v>869</v>
+      </c>
+      <c r="N71" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="O71" s="4" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15">
+      <c r="A72" t="s">
+        <v>491</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>872</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>873</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>874</v>
+      </c>
+      <c r="E72" s="2">
+        <v>0</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>875</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="I72" s="2">
+        <v>0</v>
+      </c>
+      <c r="J72" s="4" t="s">
+        <v>876</v>
+      </c>
+      <c r="K72" s="4" t="s">
+        <v>877</v>
+      </c>
+      <c r="L72" s="4" t="s">
+        <v>878</v>
+      </c>
+      <c r="M72" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="N72" s="4" t="s">
+        <v>880</v>
+      </c>
+      <c r="O72" s="4" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15">
+      <c r="A73" t="s">
+        <v>492</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>882</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>883</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>884</v>
+      </c>
+      <c r="E73" s="2">
+        <v>0</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>885</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>886</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="I73" s="2">
+        <v>0</v>
+      </c>
+      <c r="J73" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="K73" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="L73" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="M73" s="4" t="s">
+        <v>891</v>
+      </c>
+      <c r="N73" s="4" t="s">
+        <v>892</v>
+      </c>
+      <c r="O73" s="4" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15">
+      <c r="A74" t="s">
+        <v>493</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>894</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>895</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="E74" s="2">
+        <v>0</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>896</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>897</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="I74" s="2">
+        <v>0</v>
+      </c>
+      <c r="J74" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="K74" s="4" t="s">
+        <v>900</v>
+      </c>
+      <c r="L74" s="4" t="s">
+        <v>901</v>
+      </c>
+      <c r="M74" s="4" t="s">
+        <v>902</v>
+      </c>
+      <c r="N74" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="O74" s="4" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15">
+      <c r="A75" t="s">
+        <v>494</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>905</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>906</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>907</v>
+      </c>
+      <c r="E75" s="2">
+        <v>0</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>909</v>
+      </c>
+      <c r="I75" s="2">
+        <v>0</v>
+      </c>
+      <c r="J75" s="4" t="s">
+        <v>910</v>
+      </c>
+      <c r="K75" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="L75" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="M75" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="N75" s="4" t="s">
+        <v>914</v>
+      </c>
+      <c r="O75" s="4" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
+      <c r="A76" t="s">
+        <v>495</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>917</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>918</v>
+      </c>
+      <c r="E76" s="2">
+        <v>0</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="I76" s="2">
+        <v>0</v>
+      </c>
+      <c r="J76" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="K76" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="L76" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="M76" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="N76" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="O76" s="4" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15">
+      <c r="A77" t="s">
+        <v>496</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>927</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>928</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>929</v>
+      </c>
+      <c r="E77" s="2">
+        <v>0</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="I77" s="2">
+        <v>0</v>
+      </c>
+      <c r="J77" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="K77" s="4" t="s">
+        <v>934</v>
+      </c>
+      <c r="L77" s="4" t="s">
+        <v>935</v>
+      </c>
+      <c r="M77" s="4" t="s">
+        <v>936</v>
+      </c>
+      <c r="N77" s="4" t="s">
+        <v>937</v>
+      </c>
+      <c r="O77" s="4" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15">
+      <c r="A78" t="s">
+        <v>497</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>938</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>939</v>
+      </c>
+      <c r="E78" s="2">
+        <v>0</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>940</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>941</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>942</v>
+      </c>
+      <c r="I78" s="2">
+        <v>0</v>
+      </c>
+      <c r="J78" s="4" t="s">
+        <v>943</v>
+      </c>
+      <c r="K78" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="L78" s="4" t="s">
+        <v>944</v>
+      </c>
+      <c r="M78" s="4" t="s">
+        <v>945</v>
+      </c>
+      <c r="N78" s="4" t="s">
+        <v>946</v>
+      </c>
+      <c r="O78" s="4" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15">
+      <c r="A79" t="s">
+        <v>498</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>949</v>
+      </c>
+      <c r="E79" s="2">
+        <v>0</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>951</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="I79" s="2">
+        <v>0</v>
+      </c>
+      <c r="J79" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="K79" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="L79" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="M79" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="N79" s="4" t="s">
+        <v>957</v>
+      </c>
+      <c r="O79" s="4" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15">
+      <c r="A80" t="s">
+        <v>499</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>959</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>960</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="E80" s="2">
+        <v>0</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>961</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>963</v>
+      </c>
+      <c r="I80" s="2">
+        <v>0</v>
+      </c>
+      <c r="J80" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="K80" s="4" t="s">
+        <v>965</v>
+      </c>
+      <c r="L80" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="M80" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="N80" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="O80" s="4" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15">
+      <c r="A81" t="s">
+        <v>500</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>969</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>970</v>
+      </c>
+      <c r="E81" s="2">
+        <v>0</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>971</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>972</v>
+      </c>
+      <c r="I81" s="2">
+        <v>0</v>
+      </c>
+      <c r="J81" s="4" t="s">
+        <v>973</v>
+      </c>
+      <c r="K81" s="4" t="s">
+        <v>974</v>
+      </c>
+      <c r="L81" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="M81" s="4" t="s">
+        <v>975</v>
+      </c>
+      <c r="N81" s="4" t="s">
+        <v>976</v>
+      </c>
+      <c r="O81" s="4" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15">
+      <c r="A82" t="s">
+        <v>501</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>978</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>979</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="E82" s="2">
+        <v>0</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>981</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>982</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>983</v>
+      </c>
+      <c r="I82" s="2">
+        <v>0</v>
+      </c>
+      <c r="J82" s="4" t="s">
+        <v>984</v>
+      </c>
+      <c r="K82" s="4" t="s">
+        <v>985</v>
+      </c>
+      <c r="L82" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="M82" s="4" t="s">
+        <v>987</v>
+      </c>
+      <c r="N82" s="4" t="s">
+        <v>988</v>
+      </c>
+      <c r="O82" s="4" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15">
+      <c r="A83" t="s">
+        <v>502</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>991</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="E83" s="2">
+        <v>0</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>993</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>994</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>995</v>
+      </c>
+      <c r="I83" s="2">
+        <v>0</v>
+      </c>
+      <c r="J83" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="K83" s="4" t="s">
+        <v>997</v>
+      </c>
+      <c r="L83" s="4" t="s">
+        <v>998</v>
+      </c>
+      <c r="M83" s="4" t="s">
+        <v>999</v>
+      </c>
+      <c r="N83" s="4" t="s">
+        <v>1000</v>
+      </c>
+      <c r="O83" s="4" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15">
+      <c r="A84" t="s">
+        <v>503</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E84" s="2">
+        <v>0</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I84" s="2">
+        <v>0</v>
+      </c>
+      <c r="J84" s="4" t="s">
+        <v>1008</v>
+      </c>
+      <c r="K84" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="L84" s="4" t="s">
+        <v>1009</v>
+      </c>
+      <c r="M84" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="N84" s="4" t="s">
+        <v>1011</v>
+      </c>
+      <c r="O84" s="4" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15">
+      <c r="A85" t="s">
+        <v>504</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E85" s="2">
+        <v>0</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I85" s="2">
+        <v>0</v>
+      </c>
+      <c r="J85" s="4" t="s">
+        <v>1018</v>
+      </c>
+      <c r="K85" s="4" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L85" s="4" t="s">
+        <v>1020</v>
+      </c>
+      <c r="M85" s="4" t="s">
+        <v>1021</v>
+      </c>
+      <c r="N85" s="4" t="s">
+        <v>1022</v>
+      </c>
+      <c r="O85" s="4" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15">
+      <c r="A86" t="s">
+        <v>505</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E86" s="2">
+        <v>0</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G86" s="4" t="s">
+        <v>1028</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>1029</v>
+      </c>
+      <c r="I86" s="2">
+        <v>0</v>
+      </c>
+      <c r="J86" s="4" t="s">
+        <v>1030</v>
+      </c>
+      <c r="K86" s="4" t="s">
+        <v>1031</v>
+      </c>
+      <c r="L86" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="M86" s="4" t="s">
+        <v>1032</v>
+      </c>
+      <c r="N86" s="4" t="s">
+        <v>1033</v>
+      </c>
+      <c r="O86" s="4" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15">
+      <c r="A87" t="s">
+        <v>506</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E87" s="2">
+        <v>0</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="I87" s="2">
+        <v>0</v>
+      </c>
+      <c r="J87" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="K87" s="4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="L87" s="4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="M87" s="4" t="s">
+        <v>1043</v>
+      </c>
+      <c r="N87" s="4" t="s">
+        <v>1044</v>
+      </c>
+      <c r="O87" s="4" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15">
+      <c r="A88" t="s">
+        <v>507</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E88" s="2">
+        <v>0</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>1048</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>1050</v>
+      </c>
+      <c r="I88" s="2">
+        <v>0</v>
+      </c>
+      <c r="J88" s="4" t="s">
+        <v>1051</v>
+      </c>
+      <c r="K88" s="4" t="s">
+        <v>1052</v>
+      </c>
+      <c r="L88" s="4" t="s">
+        <v>1053</v>
+      </c>
+      <c r="M88" s="4" t="s">
+        <v>1054</v>
+      </c>
+      <c r="N88" s="4" t="s">
+        <v>1055</v>
+      </c>
+      <c r="O88" s="4" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15">
+      <c r="A89" t="s">
+        <v>508</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E89" s="2">
+        <v>0</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>1061</v>
+      </c>
+      <c r="I89" s="2">
+        <v>0</v>
+      </c>
+      <c r="J89" s="4" t="s">
+        <v>1062</v>
+      </c>
+      <c r="K89" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="L89" s="4" t="s">
+        <v>1064</v>
+      </c>
+      <c r="M89" s="4" t="s">
+        <v>1065</v>
+      </c>
+      <c r="N89" s="4" t="s">
+        <v>1066</v>
+      </c>
+      <c r="O89" s="4" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15">
+      <c r="A90" t="s">
+        <v>509</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E90" s="2">
+        <v>0</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>1071</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>1072</v>
+      </c>
+      <c r="I90" s="2">
+        <v>0</v>
+      </c>
+      <c r="J90" s="4" t="s">
+        <v>1073</v>
+      </c>
+      <c r="K90" s="4" t="s">
+        <v>1074</v>
+      </c>
+      <c r="L90" s="4" t="s">
+        <v>1075</v>
+      </c>
+      <c r="M90" s="4" t="s">
+        <v>1076</v>
+      </c>
+      <c r="N90" s="4" t="s">
+        <v>1077</v>
+      </c>
+      <c r="O90" s="4" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15">
+      <c r="A91" t="s">
+        <v>510</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E91" s="2">
+        <v>0</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>1082</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>1083</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="I91" s="2">
+        <v>0</v>
+      </c>
+      <c r="J91" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="K91" s="4" t="s">
+        <v>1085</v>
+      </c>
+      <c r="L91" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="M91" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="N91" s="4" t="s">
+        <v>1088</v>
+      </c>
+      <c r="O91" s="4" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15">
+      <c r="A92" t="s">
+        <v>511</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>974</v>
+      </c>
+      <c r="E92" s="2">
+        <v>0</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>1092</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>1094</v>
+      </c>
+      <c r="I92" s="2">
+        <v>0</v>
+      </c>
+      <c r="J92" s="4" t="s">
+        <v>1095</v>
+      </c>
+      <c r="K92" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="L92" s="4" t="s">
+        <v>1096</v>
+      </c>
+      <c r="M92" s="4" t="s">
+        <v>1097</v>
+      </c>
+      <c r="N92" s="4" t="s">
+        <v>1098</v>
+      </c>
+      <c r="O92" s="4" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15">
+      <c r="A93" t="s">
+        <v>512</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="E93" s="2">
+        <v>0</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>1102</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>1103</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>1104</v>
+      </c>
+      <c r="I93" s="2">
+        <v>0</v>
+      </c>
+      <c r="J93" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="K93" s="4" t="s">
+        <v>1105</v>
+      </c>
+      <c r="L93" s="4" t="s">
+        <v>1106</v>
+      </c>
+      <c r="M93" s="4" t="s">
+        <v>1107</v>
+      </c>
+      <c r="N93" s="4" t="s">
+        <v>1108</v>
+      </c>
+      <c r="O93" s="4" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15">
+      <c r="A94" t="s">
+        <v>513</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E94" s="2">
+        <v>0</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>1115</v>
+      </c>
+      <c r="I94" s="2">
+        <v>0</v>
+      </c>
+      <c r="J94" s="4" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K94" s="4" t="s">
+        <v>1117</v>
+      </c>
+      <c r="L94" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="M94" s="4" t="s">
+        <v>1118</v>
+      </c>
+      <c r="N94" s="4" t="s">
+        <v>1119</v>
+      </c>
+      <c r="O94" s="4" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15">
+      <c r="A95" t="s">
+        <v>514</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E95" s="2">
+        <v>0</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>1124</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>1125</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>1126</v>
+      </c>
+      <c r="I95" s="2">
+        <v>0</v>
+      </c>
+      <c r="J95" s="4" t="s">
+        <v>1127</v>
+      </c>
+      <c r="K95" s="4" t="s">
+        <v>1128</v>
+      </c>
+      <c r="L95" s="4" t="s">
+        <v>1129</v>
+      </c>
+      <c r="M95" s="4" t="s">
+        <v>1130</v>
+      </c>
+      <c r="N95" s="4" t="s">
+        <v>1131</v>
+      </c>
+      <c r="O95" s="4" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15">
+      <c r="A96" t="s">
+        <v>515</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E96" s="2">
+        <v>0</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>1135</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>1137</v>
+      </c>
+      <c r="I96" s="2">
+        <v>0</v>
+      </c>
+      <c r="J96" s="4" t="s">
+        <v>1138</v>
+      </c>
+      <c r="K96" s="4" t="s">
+        <v>1139</v>
+      </c>
+      <c r="L96" s="4" t="s">
+        <v>1140</v>
+      </c>
+      <c r="M96" s="4" t="s">
+        <v>1141</v>
+      </c>
+      <c r="N96" s="4" t="s">
+        <v>1142</v>
+      </c>
+      <c r="O96" s="4" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15">
+      <c r="A97" t="s">
+        <v>516</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E97" s="2">
+        <v>0</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>1147</v>
+      </c>
+      <c r="G97" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>1149</v>
+      </c>
+      <c r="I97" s="2">
+        <v>0</v>
+      </c>
+      <c r="J97" s="4" t="s">
+        <v>1150</v>
+      </c>
+      <c r="K97" s="4" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L97" s="4" t="s">
+        <v>1152</v>
+      </c>
+      <c r="M97" s="4" t="s">
+        <v>1153</v>
+      </c>
+      <c r="N97" s="4" t="s">
+        <v>1154</v>
+      </c>
+      <c r="O97" s="4" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15">
+      <c r="A98" t="s">
+        <v>517</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E98" s="2">
+        <v>0</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>1160</v>
+      </c>
+      <c r="I98" s="2">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="s">
+        <v>1161</v>
+      </c>
+      <c r="K98" s="4" t="s">
+        <v>1162</v>
+      </c>
+      <c r="L98" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="M98" s="4" t="s">
+        <v>1163</v>
+      </c>
+      <c r="N98" s="4" t="s">
+        <v>1164</v>
+      </c>
+      <c r="O98" s="4" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15">
+      <c r="A99" t="s">
+        <v>518</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E99" s="2">
+        <v>0</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>1168</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>1169</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>1170</v>
+      </c>
+      <c r="I99" s="2">
+        <v>0</v>
+      </c>
+      <c r="J99" s="4" t="s">
+        <v>1171</v>
+      </c>
+      <c r="K99" s="4" t="s">
+        <v>1172</v>
+      </c>
+      <c r="L99" s="4" t="s">
+        <v>1173</v>
+      </c>
+      <c r="M99" s="4" t="s">
+        <v>1174</v>
+      </c>
+      <c r="N99" s="4" t="s">
+        <v>1175</v>
+      </c>
+      <c r="O99" s="4" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15">
+      <c r="A100" t="s">
+        <v>519</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E100" s="2">
+        <v>0</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>1178</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>1179</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>1180</v>
+      </c>
+      <c r="I100" s="2">
+        <v>0</v>
+      </c>
+      <c r="J100" s="4" t="s">
+        <v>1181</v>
+      </c>
+      <c r="K100" s="4" t="s">
+        <v>1182</v>
+      </c>
+      <c r="L100" s="4" t="s">
+        <v>1183</v>
+      </c>
+      <c r="M100" s="4" t="s">
+        <v>1184</v>
+      </c>
+      <c r="N100" s="4" t="s">
+        <v>1185</v>
+      </c>
+      <c r="O100" s="4" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15">
+      <c r="A101" t="s">
+        <v>520</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E101" s="2">
+        <v>0</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>1190</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>1191</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>1192</v>
+      </c>
+      <c r="I101" s="2">
+        <v>0</v>
+      </c>
+      <c r="J101" s="4" t="s">
+        <v>1193</v>
+      </c>
+      <c r="K101" s="4" t="s">
+        <v>1194</v>
+      </c>
+      <c r="L101" s="4" t="s">
+        <v>1195</v>
+      </c>
+      <c r="M101" s="4" t="s">
+        <v>1196</v>
+      </c>
+      <c r="N101" s="4" t="s">
+        <v>1197</v>
+      </c>
+      <c r="O101" s="4" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15">
+      <c r="A102" t="s">
+        <v>521</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E102" s="2">
+        <v>0</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G102" s="4" t="s">
+        <v>1202</v>
+      </c>
+      <c r="H102" s="4" t="s">
+        <v>1203</v>
+      </c>
+      <c r="I102" s="2">
+        <v>0</v>
+      </c>
+      <c r="J102" s="4" t="s">
+        <v>1204</v>
+      </c>
+      <c r="K102" s="4" t="s">
+        <v>1205</v>
+      </c>
+      <c r="L102" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="M102" s="4" t="s">
+        <v>1206</v>
+      </c>
+      <c r="N102" s="4" t="s">
+        <v>1207</v>
+      </c>
+      <c r="O102" s="4" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15">
+      <c r="A103" t="s">
+        <v>522</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E103" s="2">
+        <v>0</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>1211</v>
+      </c>
+      <c r="G103" s="4" t="s">
+        <v>1212</v>
+      </c>
+      <c r="H103" s="4" t="s">
+        <v>1213</v>
+      </c>
+      <c r="I103" s="2">
+        <v>0</v>
+      </c>
+      <c r="J103" s="4" t="s">
+        <v>1214</v>
+      </c>
+      <c r="K103" s="4" t="s">
+        <v>1215</v>
+      </c>
+      <c r="L103" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="M103" s="4" t="s">
+        <v>1216</v>
+      </c>
+      <c r="N103" s="4" t="s">
+        <v>1217</v>
+      </c>
+      <c r="O103" s="4" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15">
+      <c r="A104" t="s">
+        <v>523</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E104" s="2">
+        <v>0</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>1221</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>1222</v>
+      </c>
+      <c r="H104" s="4" t="s">
+        <v>1223</v>
+      </c>
+      <c r="I104" s="2">
+        <v>0</v>
+      </c>
+      <c r="J104" s="4" t="s">
+        <v>1224</v>
+      </c>
+      <c r="K104" s="4" t="s">
+        <v>1225</v>
+      </c>
+      <c r="L104" s="4" t="s">
+        <v>1226</v>
+      </c>
+      <c r="M104" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="N104" s="4" t="s">
+        <v>1228</v>
+      </c>
+      <c r="O104" s="4" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15">
+      <c r="A105" t="s">
+        <v>524</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>1231</v>
+      </c>
+      <c r="E105" s="2">
+        <v>0</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>1158</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>1233</v>
+      </c>
+      <c r="I105" s="2">
+        <v>0</v>
+      </c>
+      <c r="J105" s="4" t="s">
+        <v>1234</v>
+      </c>
+      <c r="K105" s="4" t="s">
+        <v>1235</v>
+      </c>
+      <c r="L105" s="4" t="s">
+        <v>1236</v>
+      </c>
+      <c r="M105" s="4" t="s">
+        <v>1237</v>
+      </c>
+      <c r="N105" s="4" t="s">
+        <v>1238</v>
+      </c>
+      <c r="O105" s="4" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15">
+      <c r="A106" t="s">
+        <v>525</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>1240</v>
+      </c>
+      <c r="E106" s="2">
+        <v>0</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>1241</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>1242</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>1243</v>
+      </c>
+      <c r="I106" s="2">
+        <v>0</v>
+      </c>
+      <c r="J106" s="4" t="s">
+        <v>1244</v>
+      </c>
+      <c r="K106" s="4" t="s">
+        <v>1099</v>
+      </c>
+      <c r="L106" s="4" t="s">
+        <v>1245</v>
+      </c>
+      <c r="M106" s="4" t="s">
+        <v>1246</v>
+      </c>
+      <c r="N106" s="4" t="s">
+        <v>1247</v>
+      </c>
+      <c r="O106" s="4" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15">
+      <c r="A107" t="s">
+        <v>526</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E107" s="2">
+        <v>0</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G107" s="4" t="s">
+        <v>1253</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="I107" s="2">
+        <v>0</v>
+      </c>
+      <c r="J107" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="K107" s="4" t="s">
+        <v>1255</v>
+      </c>
+      <c r="L107" s="4" t="s">
+        <v>1256</v>
+      </c>
+      <c r="M107" s="4" t="s">
+        <v>1257</v>
+      </c>
+      <c r="N107" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="O107" s="4" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15">
+      <c r="A108" t="s">
+        <v>527</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>1260</v>
+      </c>
+      <c r="E108" s="2">
+        <v>0</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>1261</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>1262</v>
+      </c>
+      <c r="H108" s="4" t="s">
+        <v>1263</v>
+      </c>
+      <c r="I108" s="2">
+        <v>0</v>
+      </c>
+      <c r="J108" s="4" t="s">
+        <v>1264</v>
+      </c>
+      <c r="K108" s="4" t="s">
+        <v>1265</v>
+      </c>
+      <c r="L108" s="4" t="s">
+        <v>1266</v>
+      </c>
+      <c r="M108" s="4" t="s">
+        <v>1267</v>
+      </c>
+      <c r="N108" s="4" t="s">
+        <v>1268</v>
+      </c>
+      <c r="O108" s="4" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15">
+      <c r="A109" t="s">
+        <v>528</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E109" s="2">
+        <v>0</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>1273</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>1274</v>
+      </c>
+      <c r="H109" s="4" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I109" s="2">
+        <v>0</v>
+      </c>
+      <c r="J109" s="4" t="s">
+        <v>1276</v>
+      </c>
+      <c r="K109" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="L109" s="4" t="s">
+        <v>1277</v>
+      </c>
+      <c r="M109" s="4" t="s">
+        <v>1278</v>
+      </c>
+      <c r="N109" s="4" t="s">
+        <v>1279</v>
+      </c>
+      <c r="O109" s="4" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15">
+      <c r="A110" t="s">
+        <v>529</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D110" s="4" t="s">
+        <v>1283</v>
+      </c>
+      <c r="E110" s="2">
+        <v>0</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>1284</v>
+      </c>
+      <c r="G110" s="4" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H110" s="4" t="s">
+        <v>1286</v>
+      </c>
+      <c r="I110" s="2">
+        <v>0</v>
+      </c>
+      <c r="J110" s="4" t="s">
+        <v>1287</v>
+      </c>
+      <c r="K110" s="4" t="s">
+        <v>1288</v>
+      </c>
+      <c r="L110" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="M110" s="4" t="s">
+        <v>1289</v>
+      </c>
+      <c r="N110" s="4" t="s">
+        <v>1290</v>
+      </c>
+      <c r="O110" s="4" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15">
+      <c r="A111" t="s">
+        <v>530</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="E111" s="2">
+        <v>0</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>1294</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>1295</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="I111" s="2">
+        <v>0</v>
+      </c>
+      <c r="J111" s="4" t="s">
+        <v>1296</v>
+      </c>
+      <c r="K111" s="4" t="s">
+        <v>1297</v>
+      </c>
+      <c r="L111" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="M111" s="4" t="s">
+        <v>1299</v>
+      </c>
+      <c r="N111" s="4" t="s">
+        <v>1300</v>
+      </c>
+      <c r="O111" s="4" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15">
+      <c r="A112" t="s">
+        <v>531</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>831</v>
+      </c>
+      <c r="E112" s="2">
+        <v>0</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>1304</v>
+      </c>
+      <c r="G112" s="4" t="s">
+        <v>1305</v>
+      </c>
+      <c r="H112" s="4" t="s">
+        <v>1306</v>
+      </c>
+      <c r="I112" s="2">
+        <v>0</v>
+      </c>
+      <c r="J112" s="4" t="s">
+        <v>1307</v>
+      </c>
+      <c r="K112" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="L112" s="4" t="s">
+        <v>1308</v>
+      </c>
+      <c r="M112" s="4" t="s">
+        <v>1309</v>
+      </c>
+      <c r="N112" s="4" t="s">
+        <v>1310</v>
+      </c>
+      <c r="O112" s="4" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15">
+      <c r="A113" t="s">
+        <v>532</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>1313</v>
+      </c>
+      <c r="E113" s="2">
+        <v>0</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>1314</v>
+      </c>
+      <c r="G113" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="H113" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="I113" s="2">
+        <v>0</v>
+      </c>
+      <c r="J113" s="4" t="s">
+        <v>1316</v>
+      </c>
+      <c r="K113" s="4" t="s">
+        <v>1317</v>
+      </c>
+      <c r="L113" s="4" t="s">
+        <v>1318</v>
+      </c>
+      <c r="M113" s="4" t="s">
+        <v>1319</v>
+      </c>
+      <c r="N113" s="4" t="s">
+        <v>1320</v>
+      </c>
+      <c r="O113" s="4" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15">
+      <c r="A114" t="s">
+        <v>533</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>1324</v>
+      </c>
+      <c r="E114" s="2">
+        <v>0</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>1325</v>
+      </c>
+      <c r="G114" s="4" t="s">
+        <v>1326</v>
+      </c>
+      <c r="H114" s="4" t="s">
+        <v>1327</v>
+      </c>
+      <c r="I114" s="2">
+        <v>0</v>
+      </c>
+      <c r="J114" s="4" t="s">
+        <v>1328</v>
+      </c>
+      <c r="K114" s="4" t="s">
+        <v>1329</v>
+      </c>
+      <c r="L114" s="4" t="s">
+        <v>1330</v>
+      </c>
+      <c r="M114" s="4" t="s">
+        <v>1331</v>
+      </c>
+      <c r="N114" s="4" t="s">
+        <v>1332</v>
+      </c>
+      <c r="O114" s="4" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15">
+      <c r="A115" t="s">
+        <v>534</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>1335</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E115" s="2">
+        <v>0</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="G115" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="H115" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="I115" s="2">
+        <v>0</v>
+      </c>
+      <c r="J115" s="4" t="s">
+        <v>1339</v>
+      </c>
+      <c r="K115" s="4" t="s">
+        <v>1340</v>
+      </c>
+      <c r="L115" s="4" t="s">
+        <v>1341</v>
+      </c>
+      <c r="M115" s="4" t="s">
+        <v>1342</v>
+      </c>
+      <c r="N115" s="4" t="s">
+        <v>1343</v>
+      </c>
+      <c r="O115" s="4" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15">
+      <c r="A116" t="s">
+        <v>535</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>1346</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>1347</v>
+      </c>
+      <c r="E116" s="2">
+        <v>0</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>1348</v>
+      </c>
+      <c r="G116" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="H116" s="4" t="s">
+        <v>1349</v>
+      </c>
+      <c r="I116" s="2">
+        <v>0</v>
+      </c>
+      <c r="J116" s="4" t="s">
+        <v>1350</v>
+      </c>
+      <c r="K116" s="4" t="s">
+        <v>1351</v>
+      </c>
+      <c r="L116" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="M116" s="4" t="s">
+        <v>1352</v>
+      </c>
+      <c r="N116" s="4" t="s">
+        <v>1353</v>
+      </c>
+      <c r="O116" s="4" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15">
+      <c r="A117" t="s">
+        <v>536</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E117" s="2">
+        <v>0</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="H117" s="4" t="s">
+        <v>1359</v>
+      </c>
+      <c r="I117" s="2">
+        <v>0</v>
+      </c>
+      <c r="J117" s="4" t="s">
+        <v>1360</v>
+      </c>
+      <c r="K117" s="4" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L117" s="4" t="s">
+        <v>1362</v>
+      </c>
+      <c r="M117" s="4" t="s">
+        <v>1363</v>
+      </c>
+      <c r="N117" s="4" t="s">
+        <v>1364</v>
+      </c>
+      <c r="O117" s="4" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15">
+      <c r="A118" t="s">
+        <v>537</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E118" s="2">
+        <v>0</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>1367</v>
+      </c>
+      <c r="G118" s="4" t="s">
+        <v>1368</v>
+      </c>
+      <c r="H118" s="4" t="s">
+        <v>1369</v>
+      </c>
+      <c r="I118" s="2">
+        <v>0</v>
+      </c>
+      <c r="J118" s="4" t="s">
+        <v>1370</v>
+      </c>
+      <c r="K118" s="4" t="s">
+        <v>1371</v>
+      </c>
+      <c r="L118" s="4" t="s">
+        <v>1372</v>
+      </c>
+      <c r="M118" s="4" t="s">
+        <v>1373</v>
+      </c>
+      <c r="N118" s="4" t="s">
+        <v>1374</v>
+      </c>
+      <c r="O118" s="4" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15">
+      <c r="A119" t="s">
+        <v>538</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>1376</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>1377</v>
+      </c>
+      <c r="E119" s="2">
+        <v>0</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>1378</v>
+      </c>
+      <c r="G119" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="H119" s="4" t="s">
+        <v>1379</v>
+      </c>
+      <c r="I119" s="2">
+        <v>0</v>
+      </c>
+      <c r="J119" s="4" t="s">
+        <v>1380</v>
+      </c>
+      <c r="K119" s="4" t="s">
+        <v>1381</v>
+      </c>
+      <c r="L119" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="M119" s="4" t="s">
+        <v>1382</v>
+      </c>
+      <c r="N119" s="4" t="s">
+        <v>1383</v>
+      </c>
+      <c r="O119" s="4" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15">
+      <c r="A120" t="s">
+        <v>539</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>1387</v>
+      </c>
+      <c r="E120" s="2">
+        <v>0</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>1388</v>
+      </c>
+      <c r="G120" s="4" t="s">
+        <v>1389</v>
+      </c>
+      <c r="H120" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="I120" s="2">
+        <v>0</v>
+      </c>
+      <c r="J120" s="4" t="s">
+        <v>1391</v>
+      </c>
+      <c r="K120" s="4" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L120" s="4" t="s">
+        <v>1392</v>
+      </c>
+      <c r="M120" s="4" t="s">
+        <v>1393</v>
+      </c>
+      <c r="N120" s="4" t="s">
+        <v>1394</v>
+      </c>
+      <c r="O120" s="4" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15">
+      <c r="A121" t="s">
+        <v>540</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="E121" s="2">
+        <v>0</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>1398</v>
+      </c>
+      <c r="G121" s="4" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H121" s="4" t="s">
+        <v>1400</v>
+      </c>
+      <c r="I121" s="2">
+        <v>0</v>
+      </c>
+      <c r="J121" s="4" t="s">
+        <v>1401</v>
+      </c>
+      <c r="K121" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="L121" s="4" t="s">
+        <v>1403</v>
+      </c>
+      <c r="M121" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="N121" s="4" t="s">
+        <v>1404</v>
+      </c>
+      <c r="O121" s="4" t="s">
+        <v>1405</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
